--- a/Results/Main results/Main results burden shifting.xlsx
+++ b/Results/Main results/Main results burden shifting.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Results\Main results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Main results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E488327-F4C8-4F54-8AE1-AAECE061B3DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4887E21-671F-4890-AA37-541B3F2AF331}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-276" yWindow="504" windowWidth="28800" windowHeight="17496" activeTab="2" xr2:uid="{4A99E928-2974-7747-BC9A-A80C0753979A}"/>
   </bookViews>
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{565822CA-CE66-1248-8967-DD3F8E2CA5EE}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="92.296875" style="5" bestFit="1" customWidth="1"/>
@@ -959,7 +959,7 @@
         <v>38.741649096212846</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>8</v>
       </c>
@@ -974,7 +974,7 @@
         <v>53.385711881191597</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>9</v>
       </c>
@@ -989,7 +989,7 @@
         <v>0.18193831974888172</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1004,12 +1004,12 @@
         <v>1.511726716767283</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>1</v>
       </c>
@@ -1023,8 +1023,18 @@
         <f t="shared" ref="D38:D47" si="2">(B38-C38)/B38*100</f>
         <v>1.659341136040239</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F38" s="5">
+        <v>9.6372142615219423E-7</v>
+      </c>
+      <c r="G38" s="5">
+        <v>9.5054909041599411E-7</v>
+      </c>
+      <c r="H38" s="6">
+        <f t="shared" ref="H38:H47" si="3">(F38-G38)/F38*100</f>
+        <v>1.3668198484278482</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>2</v>
       </c>
@@ -1038,8 +1048,18 @@
         <f t="shared" si="2"/>
         <v>1.4301068500160641</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F39" s="5">
+        <v>9.747890256761672E-7</v>
+      </c>
+      <c r="G39" s="5">
+        <v>9.6340105535540155E-7</v>
+      </c>
+      <c r="H39" s="6">
+        <f t="shared" si="3"/>
+        <v>1.1682497464378336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1073,18 @@
         <f t="shared" si="2"/>
         <v>60.161697641448363</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F40" s="5">
+        <v>1.212261168178798E-6</v>
+      </c>
+      <c r="G40" s="5">
+        <v>5.5671217915758627E-7</v>
+      </c>
+      <c r="H40" s="5">
+        <f t="shared" si="3"/>
+        <v>54.076547713398668</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -1068,8 +1098,18 @@
         <f t="shared" si="2"/>
         <v>23.727319877538203</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F41" s="5">
+        <v>6.9472250056031953E-8</v>
+      </c>
+      <c r="G41" s="5">
+        <v>5.4758816842325259E-8</v>
+      </c>
+      <c r="H41" s="5">
+        <f t="shared" si="3"/>
+        <v>21.178863793586306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -1083,8 +1123,18 @@
         <f t="shared" si="2"/>
         <v>27.99753441941083</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F42" s="5">
+        <v>8.8649316482588085E-8</v>
+      </c>
+      <c r="G42" s="5">
+        <v>8.7951549569211961E-8</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>0.78710918601744007</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1148,18 @@
         <f t="shared" si="2"/>
         <v>29.148716400762037</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F43" s="5">
+        <v>9.5025650230216429E-8</v>
+      </c>
+      <c r="G43" s="5">
+        <v>7.0239110280375582E-8</v>
+      </c>
+      <c r="H43" s="5">
+        <f t="shared" si="3"/>
+        <v>26.084051926812467</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,8 +1173,18 @@
         <f t="shared" si="2"/>
         <v>35.807308528916586</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F44" s="5">
+        <v>1.715648132204165E-7</v>
+      </c>
+      <c r="G44" s="5">
+        <v>1.169230006116952E-7</v>
+      </c>
+      <c r="H44" s="6">
+        <f t="shared" si="3"/>
+        <v>31.8490788309376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
@@ -1128,8 +1198,18 @@
         <f t="shared" si="2"/>
         <v>39.041906298632234</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F45" s="5">
+        <v>4.1485147183785209E-7</v>
+      </c>
+      <c r="G45" s="5">
+        <v>2.5831931550448981E-7</v>
+      </c>
+      <c r="H45" s="6">
+        <f t="shared" si="3"/>
+        <v>37.732096174060118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1223,18 @@
         <f t="shared" si="2"/>
         <v>0.11273624966262892</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F46" s="5">
+        <v>9.5139123417782734E-7</v>
+      </c>
+      <c r="G46" s="5">
+        <v>9.5111121246004953E-7</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="3"/>
+        <v>2.9432867123249905E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>10</v>
       </c>
@@ -1158,13 +1248,23 @@
         <f t="shared" si="2"/>
         <v>1.0635530916650595</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F47" s="5">
+        <v>9.5307535645611104E-7</v>
+      </c>
+      <c r="G47" s="5">
+        <v>9.4495717273320371E-7</v>
+      </c>
+      <c r="H47" s="5">
+        <f t="shared" si="3"/>
+        <v>0.8517882314252424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>1</v>
       </c>
@@ -1175,11 +1275,21 @@
         <v>5.7619135211501839E-8</v>
       </c>
       <c r="D50" s="6">
-        <f t="shared" ref="D50:D59" si="3">(B50-C50)/B50*100</f>
+        <f t="shared" ref="D50:D59" si="4">(B50-C50)/B50*100</f>
         <v>16.225759299167965</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F50" s="5">
+        <v>6.8779059922807005E-8</v>
+      </c>
+      <c r="G50" s="5">
+        <v>5.7616622571315528E-8</v>
+      </c>
+      <c r="H50" s="6">
+        <f t="shared" ref="H50:H59" si="5">(F50-G50)/F50*100</f>
+        <v>16.229412504357352</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>2</v>
       </c>
@@ -1190,11 +1300,21 @@
         <v>5.7438366145523323E-8</v>
       </c>
       <c r="D51" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.050629580700075</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F51" s="5">
+        <v>6.3856329263644406E-8</v>
+      </c>
+      <c r="G51" s="5">
+        <v>5.7421162223105408E-8</v>
+      </c>
+      <c r="H51" s="6">
+        <f t="shared" si="5"/>
+        <v>10.077571189490154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>3</v>
       </c>
@@ -1205,11 +1325,21 @@
         <v>3.0864149029180787E-7</v>
       </c>
       <c r="D52" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>82.032597005791402</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F52" s="5">
+        <v>1.717785761199277E-6</v>
+      </c>
+      <c r="G52" s="5">
+        <v>3.1374588939203552E-7</v>
+      </c>
+      <c r="H52" s="5">
+        <f t="shared" si="5"/>
+        <v>81.735447080840103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>4</v>
       </c>
@@ -1220,11 +1350,21 @@
         <v>4.8388696292382393E-8</v>
       </c>
       <c r="D53" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.763779688622837</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F53" s="5">
+        <v>5.6770110307112673E-8</v>
+      </c>
+      <c r="G53" s="5">
+        <v>4.8298039344262178E-8</v>
+      </c>
+      <c r="H53" s="5">
+        <f t="shared" si="5"/>
+        <v>14.923471025542534</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -1235,11 +1375,21 @@
         <v>4.1119138925085052E-8</v>
       </c>
       <c r="D54" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.89780643202389</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F54" s="5">
+        <v>4.7756203670493298E-8</v>
+      </c>
+      <c r="G54" s="5">
+        <v>7.6326232689007158E-8</v>
+      </c>
+      <c r="H54" s="5">
+        <f t="shared" si="5"/>
+        <v>-59.824749085250616</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -1250,11 +1400,21 @@
         <v>7.4950714314015643E-8</v>
       </c>
       <c r="D55" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22.081029270426715</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F55" s="5">
+        <v>9.6190585697211898E-8</v>
+      </c>
+      <c r="G55" s="5">
+        <v>7.5062366072992407E-8</v>
+      </c>
+      <c r="H55" s="5">
+        <f t="shared" si="5"/>
+        <v>21.96495579175156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
@@ -1265,11 +1425,21 @@
         <v>1.818700170776179E-7</v>
       </c>
       <c r="D56" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.059091952676294</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F56" s="5">
+        <v>2.3948886279353269E-7</v>
+      </c>
+      <c r="G56" s="5">
+        <v>1.825072127246472E-7</v>
+      </c>
+      <c r="H56" s="6">
+        <f t="shared" si="5"/>
+        <v>23.793027117929199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>8</v>
       </c>
@@ -1280,11 +1450,21 @@
         <v>1.679211142026371E-7</v>
       </c>
       <c r="D57" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46.024219628182991</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F57" s="5">
+        <v>3.1110456031556641E-7</v>
+      </c>
+      <c r="G57" s="5">
+        <v>1.6801227928942649E-7</v>
+      </c>
+      <c r="H57" s="6">
+        <f t="shared" si="5"/>
+        <v>45.994915947550055</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
@@ -1295,11 +1475,21 @@
         <v>5.1127734483327112E-8</v>
       </c>
       <c r="D58" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-75.993332140437047</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F58" s="5">
+        <v>2.9050949749919399E-8</v>
+      </c>
+      <c r="G58" s="5">
+        <v>5.1023249700614981E-8</v>
+      </c>
+      <c r="H58" s="5">
+        <f t="shared" si="5"/>
+        <v>-75.633671669397117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,16 +1500,26 @@
         <v>5.4747777694412757E-8</v>
       </c>
       <c r="D59" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.4098811414318315</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F59" s="5">
+        <v>5.2942501325898642E-8</v>
+      </c>
+      <c r="G59" s="5">
+        <v>5.4705551984645003E-8</v>
+      </c>
+      <c r="H59" s="5">
+        <f t="shared" si="5"/>
+        <v>-3.3301234633655366</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>1</v>
       </c>
@@ -1330,11 +1530,11 @@
         <v>1.449176046629023E-2</v>
       </c>
       <c r="D62" s="6">
-        <f t="shared" ref="D62:D71" si="4">(B62-C62)/B62*100</f>
+        <f t="shared" ref="D62:D71" si="6">(B62-C62)/B62*100</f>
         <v>5.3209180857326741</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>2</v>
       </c>
@@ -1345,11 +1545,11 @@
         <v>1.468483459448219E-2</v>
       </c>
       <c r="D63" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.8492972379558439</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -1360,7 +1560,7 @@
         <v>1.8355927956233729E-2</v>
       </c>
       <c r="D64" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>79.454414745458237</v>
       </c>
     </row>
@@ -1375,7 +1575,7 @@
         <v>1.8697300933786291E-3</v>
       </c>
       <c r="D65" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20.303264587940969</v>
       </c>
     </row>
@@ -1390,7 +1590,7 @@
         <v>2.88885396550517E-3</v>
       </c>
       <c r="D66" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>19.782705298360341</v>
       </c>
     </row>
@@ -1405,7 +1605,7 @@
         <v>3.3522156470669039E-3</v>
       </c>
       <c r="D67" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26.340402205072905</v>
       </c>
     </row>
@@ -1420,7 +1620,7 @@
         <v>7.6462850862218769E-3</v>
       </c>
       <c r="D68" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>28.347081345105192</v>
       </c>
     </row>
@@ -1435,7 +1635,7 @@
         <v>7.9794463431513904E-3</v>
       </c>
       <c r="D69" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>41.468746422409836</v>
       </c>
     </row>
@@ -1450,7 +1650,7 @@
         <v>1.428783772347347E-2</v>
       </c>
       <c r="D70" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-5.8519310136417761</v>
       </c>
     </row>
@@ -1465,7 +1665,7 @@
         <v>1.4311125624827311E-2</v>
       </c>
       <c r="D71" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.2934581140660262</v>
       </c>
     </row>
@@ -1476,7 +1676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2810D38-BAE3-F947-8C7F-A3D9DE0B213F}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="92.296875" style="5" bestFit="1" customWidth="1"/>
@@ -1688,7 +1888,7 @@
         <v>25.839809546276399</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -1703,7 +1903,7 @@
         <v>36.057650200009938</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1718,7 +1918,7 @@
         <v>26.405564310013972</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1733,12 +1933,12 @@
         <v>40.724096326526961</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1753,7 +1953,7 @@
         <v>6.0049486271653425</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
@@ -1768,7 +1968,7 @@
         <v>13.373389493741369</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -1783,7 +1983,7 @@
         <v>23.853319038524319</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
@@ -1798,7 +1998,7 @@
         <v>30.780774662497951</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
@@ -1813,7 +2013,7 @@
         <v>13.102722038741527</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
@@ -1828,7 +2028,7 @@
         <v>25.384748483171382</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -1843,7 +2043,7 @@
         <v>27.119890553140596</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
@@ -1858,12 +2058,12 @@
         <v>37.977174900458607</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -1877,8 +2077,18 @@
         <f t="shared" ref="D32:D39" si="2">(B32-C32)/B32*100</f>
         <v>1.617880495533176</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F32" s="5">
+        <v>1.941409688691735E-7</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1.914751565902747E-7</v>
+      </c>
+      <c r="H32" s="6">
+        <f t="shared" ref="H32:H39" si="3">(F32-G32)/F32*100</f>
+        <v>1.3731322628224918</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +2102,18 @@
         <f t="shared" si="2"/>
         <v>3.1540334406755002</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F33" s="5">
+        <v>2.0238323490729701E-7</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1.9727406937338931E-7</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" si="3"/>
+        <v>2.5245003798106023</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -1907,8 +2127,18 @@
         <f t="shared" si="2"/>
         <v>37.339206589936886</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F34" s="5">
+        <v>2.521512917431807E-8</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1.7005509028396921E-8</v>
+      </c>
+      <c r="H34" s="5">
+        <f t="shared" si="3"/>
+        <v>32.558310882193503</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
@@ -1922,8 +2152,18 @@
         <f t="shared" si="2"/>
         <v>59.575159700096734</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F35" s="5">
+        <v>2.2634597767407621E-7</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1.053493003171827E-7</v>
+      </c>
+      <c r="H35" s="5">
+        <f t="shared" si="3"/>
+        <v>53.456517584386255</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
@@ -1937,8 +2177,18 @@
         <f t="shared" si="2"/>
         <v>38.090875477711371</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F36" s="5">
+        <v>2.859029284710304E-8</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2.2847429956673912E-8</v>
+      </c>
+      <c r="H36" s="5">
+        <f t="shared" si="3"/>
+        <v>20.086757841695327</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -1952,8 +2202,18 @@
         <f t="shared" si="2"/>
         <v>38.409817372974331</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F37" s="5">
+        <v>2.9712527580605011E-8</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1.9730040658730781E-8</v>
+      </c>
+      <c r="H37" s="5">
+        <f t="shared" si="3"/>
+        <v>33.596895769952418</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -1967,8 +2227,18 @@
         <f t="shared" si="2"/>
         <v>40.254848077891353</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F38" s="5">
+        <v>4.3183420193886442E-8</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2.7946405312521681E-8</v>
+      </c>
+      <c r="H38" s="6">
+        <f t="shared" si="3"/>
+        <v>35.28440964831659</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -1982,13 +2252,23 @@
         <f t="shared" si="2"/>
         <v>40.698965166679656</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F39" s="5">
+        <v>8.6001871878539092E-8</v>
+      </c>
+      <c r="G39" s="5">
+        <v>5.2832156598807543E-8</v>
+      </c>
+      <c r="H39" s="6">
+        <f t="shared" si="3"/>
+        <v>38.568596886562325</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
@@ -1999,11 +2279,21 @@
         <v>1.4966021794877079E-8</v>
       </c>
       <c r="D42" s="6">
-        <f t="shared" ref="D42:D49" si="3">(B42-C42)/B42*100</f>
+        <f t="shared" ref="D42:D49" si="4">(B42-C42)/B42*100</f>
         <v>20.663805295202796</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F42" s="5">
+        <v>1.88640529717417E-8</v>
+      </c>
+      <c r="G42" s="5">
+        <v>1.4954836474804879E-8</v>
+      </c>
+      <c r="H42" s="6">
+        <f t="shared" ref="H42:H49" si="5">(F42-G42)/F42*100</f>
+        <v>20.723099658343923</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
@@ -2014,11 +2304,21 @@
         <v>1.305887969704329E-8</v>
       </c>
       <c r="D43" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>44.495475040975876</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F43" s="5">
+        <v>2.3527594744183338E-8</v>
+      </c>
+      <c r="G43" s="5">
+        <v>1.3083235756286661E-8</v>
+      </c>
+      <c r="H43" s="6">
+        <f t="shared" si="5"/>
+        <v>44.39195379493183</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -2029,11 +2329,21 @@
         <v>5.057477024875804E-8</v>
       </c>
       <c r="D44" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.258172852528123</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F44" s="5">
+        <v>6.5902483858731182E-8</v>
+      </c>
+      <c r="G44" s="5">
+        <v>5.0591978887461049E-8</v>
+      </c>
+      <c r="H44" s="5">
+        <f t="shared" si="5"/>
+        <v>23.232060576183731</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>16</v>
       </c>
@@ -2044,11 +2354,21 @@
         <v>9.6379261744460552E-8</v>
       </c>
       <c r="D45" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>73.096547288400657</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F45" s="5">
+        <v>3.5824123683168359E-7</v>
+      </c>
+      <c r="G45" s="5">
+        <v>9.7310800242718316E-8</v>
+      </c>
+      <c r="H45" s="5">
+        <f t="shared" si="5"/>
+        <v>72.836516224836814</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
@@ -2059,11 +2379,21 @@
         <v>4.9295328159046487E-8</v>
       </c>
       <c r="D46" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.354530229972507</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F46" s="5">
+        <v>6.4316036299282512E-8</v>
+      </c>
+      <c r="G46" s="5">
+        <v>5.5524940889406469E-8</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="5"/>
+        <v>13.668590161508623</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
@@ -2074,11 +2404,21 @@
         <v>5.5249685395233948E-8</v>
       </c>
       <c r="D47" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.149758878295629</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F47" s="5">
+        <v>7.2840487489794382E-8</v>
+      </c>
+      <c r="G47" s="5">
+        <v>5.530250036619315E-8</v>
+      </c>
+      <c r="H47" s="5">
+        <f t="shared" si="5"/>
+        <v>24.077251166198558</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2089,11 +2429,21 @@
         <v>7.4067482579661769E-8</v>
       </c>
       <c r="D48" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.467938759979138</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F48" s="5">
+        <v>9.8060984122086844E-8</v>
+      </c>
+      <c r="G48" s="5">
+        <v>7.4212793274417057E-8</v>
+      </c>
+      <c r="H48" s="6">
+        <f t="shared" si="5"/>
+        <v>24.319754753815815</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>20</v>
       </c>
@@ -2104,16 +2454,26 @@
         <v>7.161247568696783E-8</v>
       </c>
       <c r="D49" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>35.289159844267076</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F49" s="5">
+        <v>1.1066534681766679E-7</v>
+      </c>
+      <c r="G49" s="5">
+        <v>7.1661685003641638E-8</v>
+      </c>
+      <c r="H49" s="6">
+        <f t="shared" si="5"/>
+        <v>35.244693063934399</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>13</v>
       </c>
@@ -2124,11 +2484,11 @@
         <v>3.2049999999999999E-3</v>
       </c>
       <c r="D52" s="6">
-        <f t="shared" ref="D52:D59" si="4">(B52-C52)/B52*100</f>
+        <f t="shared" ref="D52:D59" si="6">(B52-C52)/B52*100</f>
         <v>5.2101752036358517</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>14</v>
       </c>
@@ -2139,11 +2499,11 @@
         <v>2.879E-3</v>
       </c>
       <c r="D53" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>14.889302211307804</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>15</v>
       </c>
@@ -2154,11 +2514,11 @@
         <v>1.6570000000000001E-3</v>
       </c>
       <c r="D54" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31.110243793740093</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>16</v>
       </c>
@@ -2169,11 +2529,11 @@
         <v>4.5589999999999997E-3</v>
       </c>
       <c r="D55" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>74.26715355745371</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>17</v>
       </c>
@@ -2184,11 +2544,11 @@
         <v>1.8370000000000001E-3</v>
       </c>
       <c r="D56" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>30.051362908940821</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>18</v>
       </c>
@@ -2199,11 +2559,11 @@
         <v>1.918E-3</v>
       </c>
       <c r="D57" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31.33703894781814</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -2214,11 +2574,11 @@
         <v>2.6740000000000002E-3</v>
       </c>
       <c r="D58" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>30.913891180469438</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>20</v>
       </c>
@@ -2229,7 +2589,7 @@
         <v>2.7320000000000001E-3</v>
       </c>
       <c r="D59" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>37.792572153331122</v>
       </c>
     </row>
@@ -2240,10 +2600,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{641FD1B7-4A36-8C41-8D35-937375CA1B40}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="211.09765625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="11.19921875" style="5"/>
   </cols>
   <sheetData>
@@ -2446,7 +2806,7 @@
         <v>32.678237879607217</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -2461,13 +2821,13 @@
         <v>41.32394123407429</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
@@ -2475,7 +2835,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -2489,8 +2849,18 @@
         <f>(B20-C20)/B20*100</f>
         <v>1.2899961387916832</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F20" s="5">
+        <v>1.6008430481412501E-7</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1.583626297798257E-7</v>
+      </c>
+      <c r="H20" s="6">
+        <f>(F20-G20)/F20*100</f>
+        <v>1.0754802204365737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>26</v>
       </c>
@@ -2504,8 +2874,18 @@
         <f t="shared" ref="D21:D23" si="2">(B21-C21)/B21*100</f>
         <v>2.0585026246019398</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F21" s="5">
+        <v>1.6404952059371329E-7</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1.6117755423394069E-7</v>
+      </c>
+      <c r="H21" s="6">
+        <f t="shared" ref="H21:H23" si="3">(F21-G21)/F21*100</f>
+        <v>1.7506703764684182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
@@ -2519,8 +2899,18 @@
         <f t="shared" si="2"/>
         <v>36.048313607273236</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F22" s="5">
+        <v>4.5397398347855951E-8</v>
+      </c>
+      <c r="G22" s="5">
+        <v>3.1171357809009307E-8</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="3"/>
+        <v>31.336686807116376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
@@ -2534,14 +2924,24 @@
         <f t="shared" si="2"/>
         <v>38.2998397725096</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F23" s="5">
+        <v>7.9208283630545485E-8</v>
+      </c>
+      <c r="G23" s="5">
+        <v>5.0821981519335793E-8</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="3"/>
+        <v>35.837542249511564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
@@ -2549,7 +2949,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -2563,8 +2963,18 @@
         <f>(B26-C26)/B26*100</f>
         <v>29.549701870374808</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F26" s="5">
+        <v>9.3083997256603451E-9</v>
+      </c>
+      <c r="G26" s="5">
+        <v>6.5066441109407687E-9</v>
+      </c>
+      <c r="H26" s="6">
+        <f>(F26-G26)/F26*100</f>
+        <v>30.09921895592873</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2575,11 +2985,21 @@
         <v>5.5656011526741354E-9</v>
       </c>
       <c r="D27" s="6">
-        <f t="shared" ref="D27:D29" si="3">(B27-C27)/B27*100</f>
+        <f t="shared" ref="D27:D29" si="4">(B27-C27)/B27*100</f>
         <v>51.344975548125205</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F27" s="5">
+        <v>1.143890320757958E-8</v>
+      </c>
+      <c r="G27" s="5">
+        <v>5.4232238809493582E-9</v>
+      </c>
+      <c r="H27" s="6">
+        <f t="shared" ref="H27:H29" si="5">(F27-G27)/F27*100</f>
+        <v>52.589651450535456</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -2590,11 +3010,21 @@
         <v>4.5557590742507598E-8</v>
       </c>
       <c r="D28" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>30.365043940660868</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F28" s="5">
+        <v>6.5423450118480567E-8</v>
+      </c>
+      <c r="G28" s="5">
+        <v>4.5660153201017799E-8</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="5"/>
+        <v>30.208276820729925</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -2605,16 +3035,26 @@
         <v>4.3619034976213399E-8</v>
       </c>
       <c r="D29" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>42.131614368503904</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F29" s="5">
+        <v>7.5376277565401465E-8</v>
+      </c>
+      <c r="G29" s="5">
+        <v>4.364571256401586E-8</v>
+      </c>
+      <c r="H29" s="6">
+        <f t="shared" si="5"/>
+        <v>42.096221817075083</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>23</v>
       </c>
@@ -2622,7 +3062,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
@@ -2648,7 +3088,7 @@
         <v>1.7951252819264031E-3</v>
       </c>
       <c r="D33" s="6">
-        <f t="shared" ref="D33:D35" si="4">(B33-C33)/B33*100</f>
+        <f t="shared" ref="D33:D35" si="6">(B33-C33)/B33*100</f>
         <v>13.80201679429728</v>
       </c>
     </row>
@@ -2663,7 +3103,7 @@
         <v>1.8246176171766949E-3</v>
       </c>
       <c r="D34" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>35.691176939222451</v>
       </c>
     </row>
@@ -2678,7 +3118,7 @@
         <v>1.8709188697924599E-3</v>
       </c>
       <c r="D35" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>42.412924398245003</v>
       </c>
     </row>
